--- a/data/risk_metrics.xlsx
+++ b/data/risk_metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="10">
   <si>
     <t>loan_id</t>
   </si>
@@ -45,14 +45,14 @@
   <si>
     <t>L005</t>
   </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -105,11 +105,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -428,85 +429,1020 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" s="2">
+        <v>45322</v>
       </c>
       <c r="C2">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="D2">
         <v>0.35</v>
       </c>
       <c r="E2">
-        <v>25000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45351</v>
       </c>
       <c r="C3">
-        <v>0.035</v>
+        <v>0.01039733866159012</v>
       </c>
       <c r="D3">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E3">
-        <v>18000000</v>
+        <v>23000000</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45382</v>
       </c>
       <c r="C4">
-        <v>0.02</v>
+        <v>0.0107788366846173</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
-        <v>32000000</v>
+        <v>23000000</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45412</v>
       </c>
       <c r="C5">
-        <v>0.08</v>
+        <v>0.01112928494679007</v>
       </c>
       <c r="D5">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E5">
-        <v>15000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C6">
+        <v>0.01143471218179905</v>
+      </c>
+      <c r="D6">
+        <v>0.35</v>
+      </c>
+      <c r="E6">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C7">
+        <v>0.01168294196961579</v>
+      </c>
+      <c r="D7">
+        <v>0.35</v>
+      </c>
+      <c r="E7">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C8">
+        <v>0.01186407817193445</v>
+      </c>
+      <c r="D8">
+        <v>0.35</v>
+      </c>
+      <c r="E8">
+        <v>24800000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C9">
+        <v>0.01197089945997692</v>
+      </c>
+      <c r="D9">
+        <v>0.35</v>
+      </c>
+      <c r="E9">
+        <v>24600000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C10">
+        <v>0.01199914720608301</v>
+      </c>
+      <c r="D10">
+        <v>0.35</v>
+      </c>
+      <c r="E10">
+        <v>24400000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C11">
+        <v>0.01194769526175639</v>
+      </c>
+      <c r="D11">
+        <v>0.35</v>
+      </c>
+      <c r="E11">
+        <v>23200000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C12">
+        <v>0.01181859485365136</v>
+      </c>
+      <c r="D12">
+        <v>0.35</v>
+      </c>
+      <c r="E12">
+        <v>23000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C13">
+        <v>0.01161699280763918</v>
+      </c>
+      <c r="D13">
+        <v>0.35</v>
+      </c>
+      <c r="E13">
+        <v>22800000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C14">
+        <v>0.025</v>
+      </c>
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="E14">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C15">
+        <v>0.02599334665397531</v>
+      </c>
+      <c r="D15">
+        <v>0.4</v>
+      </c>
+      <c r="E15">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C16">
+        <v>0.02694709171154325</v>
+      </c>
+      <c r="D16">
+        <v>0.4</v>
+      </c>
+      <c r="E16">
+        <v>16000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C17">
+        <v>0.02782321236697518</v>
+      </c>
+      <c r="D17">
+        <v>0.4</v>
+      </c>
+      <c r="E17">
+        <v>16000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C18">
+        <v>0.02858678045449761</v>
+      </c>
+      <c r="D18">
+        <v>0.4</v>
+      </c>
+      <c r="E18">
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C19">
+        <v>0.02920735492403949</v>
+      </c>
+      <c r="D19">
+        <v>0.4</v>
+      </c>
+      <c r="E19">
+        <v>18060000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C20">
+        <v>0.02966019542983614</v>
+      </c>
+      <c r="D20">
+        <v>0.4</v>
+      </c>
+      <c r="E20">
+        <v>18120000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C21">
+        <v>0.0299272486499423</v>
+      </c>
+      <c r="D21">
+        <v>0.4</v>
+      </c>
+      <c r="E21">
+        <v>18030000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C22">
+        <v>0.02999786801520753</v>
+      </c>
+      <c r="D22">
+        <v>0.4</v>
+      </c>
+      <c r="E22">
+        <v>17880000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C23">
+        <v>0.02986923815439098</v>
+      </c>
+      <c r="D23">
+        <v>0.4</v>
+      </c>
+      <c r="E23">
+        <v>17730000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C24">
+        <v>0.02954648713412841</v>
+      </c>
+      <c r="D24">
+        <v>0.4</v>
+      </c>
+      <c r="E24">
+        <v>17580000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C25">
+        <v>0.02904248201909795</v>
+      </c>
+      <c r="D25">
+        <v>0.4</v>
+      </c>
+      <c r="E25">
+        <v>16930000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C26">
+        <v>0.018</v>
+      </c>
+      <c r="D26">
+        <v>0.3</v>
+      </c>
+      <c r="E26">
+        <v>31500000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C27">
+        <v>0.01871520959086222</v>
+      </c>
+      <c r="D27">
+        <v>0.3</v>
+      </c>
+      <c r="E27">
+        <v>31000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C28">
+        <v>0.01940190603231114</v>
+      </c>
+      <c r="D28">
+        <v>0.3</v>
+      </c>
+      <c r="E28">
+        <v>30500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C29">
+        <v>0.02003271290422213</v>
+      </c>
+      <c r="D29">
+        <v>0.3</v>
+      </c>
+      <c r="E29">
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C30">
+        <v>0.02058248192723828</v>
+      </c>
+      <c r="D30">
+        <v>0.3</v>
+      </c>
+      <c r="E30">
+        <v>29500000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C31">
+        <v>0.02102929554530843</v>
+      </c>
+      <c r="D31">
+        <v>0.3</v>
+      </c>
+      <c r="E31">
+        <v>29000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C32">
+        <v>0.02135534070948202</v>
+      </c>
+      <c r="D32">
+        <v>0.3</v>
+      </c>
+      <c r="E32">
+        <v>28500000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C33">
+        <v>0.02154761902795846</v>
+      </c>
+      <c r="D33">
+        <v>0.3</v>
+      </c>
+      <c r="E33">
+        <v>28000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C34">
+        <v>0.02159846497094942</v>
+      </c>
+      <c r="D34">
+        <v>0.3</v>
+      </c>
+      <c r="E34">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C35">
+        <v>0.0215058514711615</v>
+      </c>
+      <c r="D35">
+        <v>0.3</v>
+      </c>
+      <c r="E35">
+        <v>25500000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C36">
+        <v>0.02127347073657245</v>
+      </c>
+      <c r="D36">
+        <v>0.3</v>
+      </c>
+      <c r="E36">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C37">
+        <v>0.02091058705375052</v>
+      </c>
+      <c r="D37">
+        <v>0.3</v>
+      </c>
+      <c r="E37">
+        <v>24500000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C38">
+        <v>0.05</v>
+      </c>
+      <c r="D38">
+        <v>0.45</v>
+      </c>
+      <c r="E38">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C39">
+        <v>0.05363636363636364</v>
+      </c>
+      <c r="D39">
+        <v>0.45</v>
+      </c>
+      <c r="E39">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C40">
+        <v>0.05727272727272728</v>
+      </c>
+      <c r="D40">
+        <v>0.45</v>
+      </c>
+      <c r="E40">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C41">
+        <v>0.06090909090909091</v>
+      </c>
+      <c r="D41">
+        <v>0.45</v>
+      </c>
+      <c r="E41">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C42">
+        <v>0.06454545454545456</v>
+      </c>
+      <c r="D42">
+        <v>0.45</v>
+      </c>
+      <c r="E42">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C43">
+        <v>0.06818181818181819</v>
+      </c>
+      <c r="D43">
+        <v>0.45</v>
+      </c>
+      <c r="E43">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C44">
+        <v>0.07181818181818182</v>
+      </c>
+      <c r="D44">
+        <v>0.45</v>
+      </c>
+      <c r="E44">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C45">
+        <v>0.07545454545454547</v>
+      </c>
+      <c r="D45">
+        <v>0.45</v>
+      </c>
+      <c r="E45">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C46">
+        <v>0.0890909090909091</v>
+      </c>
+      <c r="D46">
+        <v>0.45</v>
+      </c>
+      <c r="E46">
+        <v>13120000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C47">
+        <v>0.09272727272727274</v>
+      </c>
+      <c r="D47">
+        <v>0.45</v>
+      </c>
+      <c r="E47">
+        <v>13240000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C48">
+        <v>0.09636363636363636</v>
+      </c>
+      <c r="D48">
+        <v>0.45</v>
+      </c>
+      <c r="E48">
+        <v>13360000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C49">
+        <v>0.1</v>
+      </c>
+      <c r="D49">
+        <v>0.45</v>
+      </c>
+      <c r="E49">
+        <v>13480000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>0.015</v>
-      </c>
-      <c r="D6">
+      <c r="B50" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C50">
+        <v>0.012</v>
+      </c>
+      <c r="D50">
         <v>0.33</v>
       </c>
-      <c r="E6">
-        <v>22000000</v>
+      <c r="E50">
+        <v>21750000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C51">
+        <v>0.01247680639390815</v>
+      </c>
+      <c r="D51">
+        <v>0.33</v>
+      </c>
+      <c r="E51">
+        <v>21500000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C52">
+        <v>0.01293460402154076</v>
+      </c>
+      <c r="D52">
+        <v>0.33</v>
+      </c>
+      <c r="E52">
+        <v>21250000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C53">
+        <v>0.01335514193614808</v>
+      </c>
+      <c r="D53">
+        <v>0.33</v>
+      </c>
+      <c r="E53">
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C54">
+        <v>0.01372165461815885</v>
+      </c>
+      <c r="D54">
+        <v>0.33</v>
+      </c>
+      <c r="E54">
+        <v>20750000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C55">
+        <v>0.01401953036353895</v>
+      </c>
+      <c r="D55">
+        <v>0.33</v>
+      </c>
+      <c r="E55">
+        <v>20500000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C56">
+        <v>0.01423689380632135</v>
+      </c>
+      <c r="D56">
+        <v>0.33</v>
+      </c>
+      <c r="E56">
+        <v>19450000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C57">
+        <v>0.0143650793519723</v>
+      </c>
+      <c r="D57">
+        <v>0.33</v>
+      </c>
+      <c r="E57">
+        <v>19200000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C58">
+        <v>0.01439897664729961</v>
+      </c>
+      <c r="D58">
+        <v>0.33</v>
+      </c>
+      <c r="E58">
+        <v>18950000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C59">
+        <v>0.01433723431410767</v>
+      </c>
+      <c r="D59">
+        <v>0.33</v>
+      </c>
+      <c r="E59">
+        <v>18700000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C60">
+        <v>0.01418231382438164</v>
+      </c>
+      <c r="D60">
+        <v>0.33</v>
+      </c>
+      <c r="E60">
+        <v>18450000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C61">
+        <v>0.01394039136916702</v>
+      </c>
+      <c r="D61">
+        <v>0.33</v>
+      </c>
+      <c r="E61">
+        <v>18200000</v>
       </c>
     </row>
   </sheetData>
